--- a/data/trans_camb/IP11A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP11A_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>12,38</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25,93</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23,97</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>23,17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,85</t>
+          <t>11,52</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 56,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 78,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 76,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,02</t>
+          <t>0,0; 45,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,1</t>
+          <t>0,0; 32,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,24</t>
+          <t>0,0; 52,55</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>18,42</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32,75</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13,48</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,48</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21,33</t>
+          <t>19,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 46,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 80,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 53,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,39</t>
+          <t>0,0; 28,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,44</t>
+          <t>0,0; 29,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,97</t>
+          <t>0,0; 55,15</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31,45</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>33,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,35</t>
+          <t>17,28</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,18</t>
+          <t>0,0; 75,62</t>
         </is>
       </c>
     </row>
@@ -1172,22 +1172,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1488,27 +1488,27 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>33,98</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1541,24 +1541,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,46</t>
+          <t>0,0; 68,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1594,22 +1594,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1709,22 +1709,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>18,06</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1762,24 +1762,24 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>0,0; 77,62</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,91</t>
+          <t>0,0; 35,18</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1815,22 +1815,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-5,51</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>12,71</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-5,51</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>28,98</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-5,51</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>12,71</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-5,51</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-27,87; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>-11,06; 57,77</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>-28,08; 0,0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>0,0; 80,17</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>-29,98; 0,0</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>-10,99; 65,38</t>
-        </is>
-      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 0,0</t>
+          <t>-16,34; 0,0</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 52,87</t>
+          <t>-3,48; 51,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 0,0</t>
+          <t>-17,54; 0,0</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>230,56%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>230,56%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-13,85</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-5,73</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-13,85</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-13,85</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-5,73</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-13,85</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-43,08; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-30,52; 17,33</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 17,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2219,17 +2219,17 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 0,0</t>
+          <t>-25,88; 0,0</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-18,94; 16,69</t>
+          <t>-17,56; 13,37</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 0,0</t>
+          <t>-30,2; 0,0</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-41,39%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-41,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,49</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>3,07</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>1,37</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>11,77</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>7,83</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,97</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>-6,08; 5,61</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3,27; 26,87</t>
+          <t>-6,41; 6,36</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>-4,26; 21,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 5,32</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 6,6</t>
+          <t>3,33; 26,61</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 20,77</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,02</t>
+          <t>-3,19; 4,39</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 10,27</t>
+          <t>-0,57; 10,45</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 15,73</t>
+          <t>-0,78; 14,75</t>
         </is>
       </c>
     </row>
@@ -2458,34 +2458,34 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-12,46%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-18,59%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>78,3%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-12,46%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-18,59%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>15,74%</t>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>232,36%</t>
+          <t>222,53%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-45,16; —</t>
+          <t>-51,15; 2258,29</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
